--- a/static/fixtures/sample.xlsx
+++ b/static/fixtures/sample.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Notes" sheetId="3" r:id="rId3"/>
+    <sheet name="Lanes" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -509,6 +510,7 @@
         <v>Total SKUs</v>
       </c>
       <c r="B2">
+        <f>COUNTA(Inventory!A2:A6)</f>
         <v>5</v>
       </c>
     </row>
@@ -517,6 +519,7 @@
         <v>Total units</v>
       </c>
       <c r="B3">
+        <f>SUM(Inventory!C2:C6)</f>
         <v>787</v>
       </c>
     </row>
@@ -580,4 +583,61 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:D6"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>Lane</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Loads</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Miles</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>Reno-Austin</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="str">
+        <v>Austin-Reno</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>Total</v>
+      </c>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <f>SUM(D3:D5)</f>
+        <v>3300</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="B2:D6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/static/fixtures/sample.xlsx
+++ b/static/fixtures/sample.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Notes" sheetId="3" r:id="rId3"/>
     <sheet name="Lanes" sheetId="4" r:id="rId4"/>
+    <sheet name="Checks" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -640,4 +641,48 @@
     <ignoredError numberStoredAsText="1" sqref="B2:D6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>=abc</v>
+      </c>
+      <c r="B1">
+        <v>10</v>
+      </c>
+      <c r="C1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>5</v>
+      </c>
+      <c r="E1">
+        <f>SUM(B1:D1)</f>
+        <v>10</v>
+      </c>
+      <c r="F1">
+        <f>B1*2</f>
+        <v>999</v>
+      </c>
+      <c r="G1" t="b">
+        <f>1=1</f>
+        <v>1</v>
+      </c>
+      <c r="H1" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I1" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
 </file>